--- a/student_data.xlsx
+++ b/student_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\xampp\htdocs\wasscecass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8048969C-7179-4A5E-970C-4FB14A3D8C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED173D3-3E30-4188-BB58-2E29BE0EA37A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="WAEC Registration" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WAEC Registration'!$A$1:$N$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WAEC Registration'!$A$1:$M$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'WAEC Registration'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -75,40 +75,40 @@
     <t>SUBJECT 4</t>
   </si>
   <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>VISUAL ARTS</t>
-  </si>
-  <si>
-    <t>BASKETRY</t>
-  </si>
-  <si>
-    <t>SHADRACK</t>
-  </si>
-  <si>
-    <t>YAWSON</t>
-  </si>
-  <si>
-    <t>ICT (ELECT)</t>
-  </si>
-  <si>
     <t>GEN KNOW IN ART</t>
   </si>
   <si>
-    <t>GRAPHIC DESIGN</t>
-  </si>
-  <si>
-    <t>Age</t>
-  </si>
-  <si>
     <t>Fullname</t>
   </si>
   <si>
-    <t>0314065057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YAWSON SHADRACK </t>
+    <t>BESSAH</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>MAWUSE</t>
+  </si>
+  <si>
+    <t>BESSAH VANESSA MAWUSE</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>HOME ECONOMICS</t>
+  </si>
+  <si>
+    <t>CLOTHING &amp; TEXTILES</t>
+  </si>
+  <si>
+    <t>FRENCH</t>
+  </si>
+  <si>
+    <t>0306013034</t>
+  </si>
+  <si>
+    <t>MGT IN LIVING</t>
   </si>
 </sst>
 </file>
@@ -126,6 +126,7 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -542,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.54296875" customWidth="1"/>
@@ -550,17 +551,16 @@
     <col min="3" max="3" width="18.7265625" customWidth="1"/>
     <col min="4" max="4" width="34.36328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.81640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.7265625" customWidth="1"/>
-    <col min="7" max="7" width="10.453125" customWidth="1"/>
-    <col min="8" max="8" width="31.7265625" customWidth="1"/>
-    <col min="9" max="9" width="30.81640625" customWidth="1"/>
-    <col min="10" max="10" width="16.90625" style="6" customWidth="1"/>
-    <col min="11" max="11" width="22.08984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="21.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.453125" customWidth="1"/>
+    <col min="7" max="7" width="31.7265625" customWidth="1"/>
+    <col min="8" max="8" width="30.81640625" customWidth="1"/>
+    <col min="9" max="9" width="16.90625" style="6" customWidth="1"/>
+    <col min="10" max="10" width="22.08984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="21.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -571,84 +571,79 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="K1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="L1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="M1" s="11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="2"/>
+      <c r="C2" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="D2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="13">
+        <v>38943</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="2">
+        <v>2023</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="13">
-        <v>37769</v>
-      </c>
-      <c r="F2" s="2">
-        <f t="shared" ref="F2" ca="1" si="0">DATEDIF(E2, TODAY(), "Y")</f>
-        <v>22</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="K2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="12" t="s">
         <v>12</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="2">
-        <v>2023</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="N2" s="12" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:M2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup scale="56" orientation="landscape" r:id="rId1"/>
